--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486549_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486549_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7709</v>
+        <v>6.7989</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7455</v>
+        <v>4.3728</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0254</v>
+        <v>2.4261</v>
       </c>
       <c r="G2" t="n">
         <v>5.6068</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2879</v>
+        <v>-0.2599</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7174</v>
+        <v>-0.0901</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5705</v>
+        <v>-0.1698</v>
       </c>
       <c r="V2" t="n">
         <v>1.017</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5602</v>
+        <v>1.6113</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9482</v>
+        <v>0.1227</v>
       </c>
       <c r="F3" t="n">
-        <v>1.612</v>
+        <v>1.4887</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1064</v>
@@ -688,13 +688,13 @@
         <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8189</v>
+        <v>0.87</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8857</v>
+        <v>0.0601</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9332</v>
+        <v>0.8099</v>
       </c>
       <c r="V3" t="n">
         <v>0.1952</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.168</v>
+        <v>1.3698</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6722</v>
+        <v>1.6532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4957</v>
+        <v>-0.2833</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2913</v>
+        <v>1.2791</v>
       </c>
       <c r="H4" t="n">
-        <v>1.104</v>
+        <v>0.8726</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1873</v>
+        <v>0.4064</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8777</v>
+        <v>1.8387</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8395</v>
+        <v>1.6059</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0382</v>
+        <v>0.2327</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4136</v>
+        <v>-0.5596</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2645</v>
+        <v>-0.7333</v>
       </c>
       <c r="O4" t="n">
-        <v>0.149</v>
+        <v>0.1737</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1233</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2055</v>
+        <v>-0.2704</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0822</v>
+        <v>0.7739</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8406</v>
+        <v>1.2913</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0007</v>
+        <v>0.6722</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.16</v>
+        <v>0.619</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2791</v>
+        <v>1.2913</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8726</v>
+        <v>1.104</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4064</v>
+        <v>0.1873</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8387</v>
+        <v>0.8777</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6059</v>
+        <v>0.8395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2327</v>
+        <v>0.0382</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5596</v>
+        <v>0.4136</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7333</v>
+        <v>0.2645</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1737</v>
+        <v>0.149</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9576</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0257</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-0.2055</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8972</v>
+        <v>0.2055</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5785</v>
+        <v>0.6433</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1361</v>
+        <v>0.5399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4424</v>
+        <v>0.1034</v>
       </c>
       <c r="G6" t="n">
         <v>2.0614</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2176</v>
+        <v>-0.1529</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4554</v>
+        <v>-0.0517</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2378</v>
+        <v>-0.1013</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0477</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3543</v>
+        <v>0.4297</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0875</v>
+        <v>-1.9505</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4419</v>
+        <v>2.3802</v>
       </c>
       <c r="G7" t="n">
         <v>0.0201</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4864</v>
+        <v>0.5618</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2704</v>
+        <v>-0.1334</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7568</v>
+        <v>0.6952</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3698</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0891</v>
+        <v>0.152</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7159</v>
+        <v>-1.6221</v>
       </c>
       <c r="F8" t="n">
-        <v>1.805</v>
+        <v>1.7742</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3772</v>
@@ -1078,13 +1078,13 @@
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.226</v>
+        <v>-0.1631</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1093</v>
+        <v>-0.0156</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1167</v>
+        <v>-0.1475</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0477</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.059</v>
+        <v>-0.1769</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7627</v>
+        <v>3.4959</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7037</v>
+        <v>-3.6729</v>
       </c>
       <c r="G9" t="n">
         <v>1.2656</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2056</v>
+        <v>-0.0303</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6682</v>
+        <v>0.4014</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4625</v>
+        <v>-0.4317</v>
       </c>
       <c r="V9" t="n">
         <v>-2.0647</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4571</v>
+        <v>-1.6853</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6074</v>
+        <v>-1.6507</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1503</v>
+        <v>-0.0347</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3338</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5292</v>
+        <v>0.301</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1971</v>
+        <v>0.1538</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3321</v>
+        <v>0.1472</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8788</v>
+        <v>-2.9298</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8726</v>
+        <v>-2.1394</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0062</v>
+        <v>-0.7904</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4612</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1746</v>
+        <v>-0.2256</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4266</v>
+        <v>0.1598</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6012</v>
+        <v>-0.3854</v>
       </c>
       <c r="V11" t="n">
         <v>-1.243</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0687</v>
+        <v>-4.4607</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.337</v>
+        <v>-4.8215</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2684</v>
+        <v>0.3608</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9107</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5224</v>
+        <v>0.0856</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8904</v>
+        <v>-0.3749</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3681</v>
+        <v>0.4605</v>
       </c>
       <c r="V12" t="n">
         <v>-0.113</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.015999999999998</v>
+        <v>3.043599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.355</v>
+        <v>-1.327500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3712</v>
+        <v>4.3711</v>
       </c>
       <c r="G13" t="n">
         <v>5.335000000000001</v>
@@ -1468,10 +1468,10 @@
         <v>10.8752</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4626</v>
+        <v>1.4901</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3937</v>
+        <v>-0.3665</v>
       </c>
       <c r="U13" t="n">
         <v>1.8565</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8898</v>
+        <v>5.0343</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5909</v>
+        <v>3.9204</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2989</v>
+        <v>1.114</v>
       </c>
       <c r="G14" t="n">
         <v>2.6358</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5362</v>
+        <v>0.6808</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8736</v>
+        <v>0.2031</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6626</v>
+        <v>0.4777</v>
       </c>
       <c r="V14" t="n">
         <v>0.1952</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4739</v>
+        <v>2.6473</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8403</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6336</v>
+        <v>1.6952</v>
       </c>
       <c r="G15" t="n">
         <v>0.671</v>
@@ -1624,13 +1624,13 @@
         <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2586</v>
+        <v>0.432</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1286</v>
+        <v>0.2403</v>
       </c>
       <c r="U15" t="n">
-        <v>0.13</v>
+        <v>0.1917</v>
       </c>
       <c r="V15" t="n">
         <v>1.1093</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0622</v>
+        <v>2.4494</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6409</v>
+        <v>2.088</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5788</v>
+        <v>0.3615</v>
       </c>
       <c r="G16" t="n">
         <v>1.1057</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4557</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6249</v>
+        <v>-0.1778</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8309</v>
+        <v>0.1093</v>
       </c>
       <c r="V16" t="n">
         <v>2.0647</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.122</v>
+        <v>0.3013</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7695</v>
+        <v>1.6337</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6475</v>
+        <v>-1.3324</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2625</v>
+        <v>0.0115</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9646</v>
+        <v>-2.0317</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7020999999999999</v>
+        <v>2.0432</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7902</v>
+        <v>0.7176</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7519</v>
+        <v>-1.2164</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0382</v>
+        <v>1.934</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.7062</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2127</v>
+        <v>-0.8153</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7403</v>
+        <v>0.1091</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9693000000000001</v>
+        <v>-0.1027</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3942</v>
+        <v>-0.2139</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.1111</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0327</v>
+        <v>-0.1352</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6337</v>
+        <v>-0.5405</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6664</v>
+        <v>0.4053</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0115</v>
+        <v>-1.1743</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0317</v>
+        <v>-0.7057</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0432</v>
+        <v>-0.4686</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7176</v>
+        <v>-0.6156</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2164</v>
+        <v>-0.6538</v>
       </c>
       <c r="L18" t="n">
-        <v>1.934</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7062</v>
+        <v>-0.5587</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8153</v>
+        <v>-0.0519</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1091</v>
+        <v>-0.5068</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4367</v>
+        <v>0.4089</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2139</v>
+        <v>-0.1202</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2228</v>
+        <v>0.529</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4396</v>
+        <v>-0.4213</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4287</v>
+        <v>0.2107</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0109</v>
+        <v>-0.632</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1743</v>
+        <v>1.2625</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7057</v>
+        <v>1.9646</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4686</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6156</v>
+        <v>1.7902</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6538</v>
+        <v>1.7519</v>
       </c>
       <c r="L19" t="n">
         <v>0.0382</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5587</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0519</v>
+        <v>0.2127</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5068</v>
+        <v>-0.7403</v>
       </c>
       <c r="P19" t="n">
-        <v>0.435</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1044</v>
+        <v>0.426</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1646</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1128</v>
+        <v>0.5906</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5201</v>
+        <v>-0.4276</v>
       </c>
       <c r="E20" t="n">
         <v>-0.8638</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3437</v>
+        <v>0.4362</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6623</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.0171</v>
       </c>
       <c r="T20" t="n">
         <v>-0.137</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8893</v>
+        <v>-1.5398</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2226</v>
+        <v>-2.7756</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3333</v>
+        <v>1.2357</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6768</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2125</v>
+        <v>0.137</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0274</v>
+        <v>-0.5804</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7174</v>
       </c>
       <c r="V21" t="n">
         <v>0.5649999999999999</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9909</v>
+        <v>-3.8165</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2246</v>
+        <v>-4.7715</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2337</v>
+        <v>0.9549</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0041</v>
+        <v>-2.5039</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.666</v>
+        <v>0.0668</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.338</v>
+        <v>-2.5707</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.2294</v>
+        <v>-0.7482</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2492</v>
+        <v>0.5506</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.9802</v>
+        <v>-1.2989</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-1.7556</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4169</v>
+        <v>-0.4838</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3578</v>
+        <v>-1.2718</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5225</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0359</v>
+        <v>-0.3121</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1454</v>
+        <v>-0.7607</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1813</v>
+        <v>0.4485</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4997</v>
+        <v>0.7395</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1745</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6913</v>
+        <v>-3.8728</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1068</v>
+        <v>-4.2246</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4154</v>
+        <v>0.3519</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5039</v>
+        <v>-4.0041</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0668</v>
+        <v>-0.666</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5707</v>
+        <v>-3.338</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7482</v>
+        <v>-3.2294</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5506</v>
+        <v>-0.2492</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2989</v>
+        <v>-2.9802</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7556</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4838</v>
+        <v>-0.4169</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2718</v>
+        <v>-0.3578</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7401</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1869</v>
+        <v>0.1541</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0959</v>
+        <v>-0.1454</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.091</v>
+        <v>0.2995</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7395</v>
+        <v>1.4997</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X23" t="n">
-        <v>0.7395</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.016</v>
+        <v>0.2190999999999992</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.371199999999999</v>
+        <v>-4.371099999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>2.355</v>
+        <v>4.5903</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.3349</v>
+        <v>-5.334900000000001</v>
       </c>
       <c r="H24" t="n">
         <v>1.9922</v>
@@ -2302,13 +2302,13 @@
         <v>1.734599999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>6.3282</v>
+        <v>6.328200000000001</v>
       </c>
       <c r="L24" t="n">
         <v>-4.5939</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.069700000000001</v>
+        <v>-7.0697</v>
       </c>
       <c r="N24" t="n">
         <v>-4.336</v>
@@ -2323,16 +2323,16 @@
         <v>-10.8754</v>
       </c>
       <c r="R24" t="n">
-        <v>9.787500000000001</v>
+        <v>9.787499999999998</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4627</v>
+        <v>1.7726</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.8565</v>
+        <v>-1.8566</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3937</v>
+        <v>3.628900000000001</v>
       </c>
       <c r="V24" t="n">
         <v>4.8688</v>
